--- a/Sample_run/1/student/dungdvhe181404/TC4/GradeDetail.xlsx
+++ b/Sample_run/1/student/dungdvhe181404/TC4/GradeDetail.xlsx
@@ -201,6 +201,12 @@
   </x:si>
   <x:si>
     <x:t>Client closing connection</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIL</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -227,7 +233,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -242,6 +248,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFF00"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFB6C1"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -264,7 +275,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="4">
+  <x:cellStyleXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -277,8 +288,11 @@
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -292,6 +306,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -931,7 +949,7 @@
     <x:col min="8" max="8" width="152.853482" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="10.853482" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="29.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
@@ -1044,7 +1062,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>40724</x:v>
+        <x:v>55164</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1103,7 +1121,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>40724</x:v>
+        <x:v>55164</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1156,7 +1174,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>40724</x:v>
+        <x:v>55164</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1212,7 +1230,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>40724</x:v>
+        <x:v>55164</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1271,7 +1289,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>40724</x:v>
+        <x:v>55164</x:v>
       </x:c>
       <x:c r="R6" s="2" t="s">
         <x:v>46</x:v>
@@ -1327,7 +1345,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>40724</x:v>
+        <x:v>55164</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
         <x:v>56</x:v>
@@ -1380,7 +1398,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>40724</x:v>
+        <x:v>55164</x:v>
       </x:c>
       <x:c r="Q8" s="0">
         <x:v>4000</x:v>
@@ -1439,7 +1457,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>40724</x:v>
+        <x:v>55164</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>56</x:v>
@@ -1483,22 +1501,22 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="O10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>40724</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R10" s="3" t="s">
-        <x:v>56</x:v>
+        <x:v>55164</x:v>
+      </x:c>
+      <x:c r="R10" s="2" t="s">
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:18">
@@ -1548,7 +1566,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>40724</x:v>
+        <x:v>55164</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>
@@ -1589,28 +1607,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M12" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N12" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O12" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P12" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q12" s="0">
-        <x:v>40724</x:v>
-      </x:c>
-      <x:c r="R12" s="3" t="s">
-        <x:v>56</x:v>
+      <x:c r="P12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R12" s="4" t="s">
+        <x:v>62</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
